--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1399,6 +1399,116 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125910985</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogstorp, Bäckebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>565464</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6305134</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Olof Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olof Persson, Jesper Haraldsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olof Persson, Jesper Haraldsson</t>
+          <t>Jesper Haraldsson, Olof Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jesper Haraldsson, Olof Persson</t>
+          <t>Olof Persson, Jesper Haraldsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -1404,7 +1404,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99909463</v>
+        <v>99909358</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565463.3317085528</v>
+        <v>565476</v>
       </c>
       <c r="R2" t="n">
-        <v>6305132.787501801</v>
+        <v>6305135</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,19 +751,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>99909395</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565471.2930534594</v>
+        <v>565471</v>
       </c>
       <c r="R3" t="n">
-        <v>6305148.75762016</v>
+        <v>6305149</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +857,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99909358</v>
+        <v>99909427</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -965,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565476.4422769872</v>
+        <v>565458</v>
       </c>
       <c r="R4" t="n">
-        <v>6305134.632599435</v>
+        <v>6305138</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,19 +963,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99909582</v>
+        <v>99909463</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1086,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565492.4526568783</v>
+        <v>565463</v>
       </c>
       <c r="R5" t="n">
-        <v>6305126.142032959</v>
+        <v>6305132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,19 +1069,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,12 +1102,7 @@
         <v>99909536</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565477.2213319698</v>
+        <v>565478</v>
       </c>
       <c r="R6" t="n">
-        <v>6305119.892492405</v>
+        <v>6305120</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,19 +1175,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99909427</v>
+        <v>99909582</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1235,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1328,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565458.3112179126</v>
+        <v>565492</v>
       </c>
       <c r="R7" t="n">
-        <v>6305138.718849109</v>
+        <v>6305126</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,19 +1281,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1314,7 @@
         <v>125910985</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 13690-2022 artfynd.xlsx
+++ b/artfynd/A 13690-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99909358</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99909395</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99909427</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99909463</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99909536</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99909582</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,8 +1453,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125910985</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>